--- a/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_Phan_03_22_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_Phan_03_22_Cau.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Score 100 nghĩa bằng reference cost.</t>
+          <t>Score = min(150, 100 * reference / team) = min(150, 100 * (100 / 200)) = min(150, 50) = 50 điểm.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -689,7 +689,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ lấy private instance theo contract.</t>
+          <t>Điểm chính thức xếp hạng chỉ tính trên các private instance theo quy định: (120 + 90 + 150) / 3 = 360 / 3 = 120 điểm.</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -737,7 +737,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số gồm toàn bộ private instance bắt buộc.</t>
+          <t>Điểm trung bình private của cả 4 instances bắt buộc (kể cả instance thiếu bị 0 điểm): (150 + 110 + 0 + 90) / 4 = 350 / 4 = 87,5 điểm.</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không dùng distance-only delta nếu working cost còn term downstream.</t>
+          <t>Các vị trí chèn khả thi có working-cost delta lần lượt là 12, 7, 9. Delta nhỏ nhất của cheapest feasible insertion là min(12, 7, 9) = 7.</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -984,7 +984,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính chênh second-best trừ best cho từng order.</t>
+          <t>Regret = second-best insertion cost - best insertion cost. Order A: 9 - 4 = 5; Order B: 20 - 6 = 14; Order C: 11 - 5 = 6. Regret lớn nhất = max(5, 14, 6) = 14.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1142,7 +1142,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính load mỗi route sau swap, không chỉ tổng toàn fleet.</t>
+          <t>Đánh giá bước hoán đổi (swap): (a) Tải trọng mới của R1 là 10 - 8 + 2 = 4, của R2 là 6 - 2 + 8 = 12; (b) Lời giải bị vi phạm ràng buộc cứng (hard-invalid) vì R2 bị quá tải 2 đơn vị (12 &gt; capacity 10); (c) Mức giảm quãng đường không thể bù đắp vi phạm ràng buộc tải trọng cứng.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.607</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1301,7 +1301,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Move tốt hơn nhận trực tiếp; move xấu dùng exponent âm.</t>
+          <t>Xác suất chấp nhận move xấu trong Simulated Annealing: P = exp(-Δ / T) = exp(-5 / 10) = exp(-0,5) ≈ 0,60653..., làm tròn 3 chữ số là 0,607.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ end-to-end reserve trước khi chia cho instance.</t>
+          <t>Tổng thời gian 30 phút, trừ thời gian dự phòng cố định (reserve) 6 phút, còn lại 30 - 6 = 24 phút. Chia đều cho 8 instances: 24 / 8 = 3 phút/instance.</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1451,7 +1451,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ mọi reserve end-to-end trước khi chia.</t>
+          <t>Tổng thời gian 42 phút. Tổng reserve: 7 phút cố định + 5 phút riêng cho instance cuối = 12 phút. Thời gian còn lại cho 4 instances đầu: 42 - 12 = 30 phút. Chia đều cho 4 instances: 30 / 4 = 7,5 phút/instance.</t>
         </is>
       </c>
     </row>
